--- a/data/lossofsale_sg_trivandrum.xlsx
+++ b/data/lossofsale_sg_trivandrum.xlsx
@@ -2634,6 +2634,564 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="65">
+        <v>48</v>
+      </c>
+      <c t="inlineStr" r="B50">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C50">
+        <is>
+          <t xml:space="preserve">mathew</t>
+        </is>
+      </c>
+      <c r="D50" s="65">
+        <v>7025572372</v>
+      </c>
+      <c t="inlineStr" r="E50">
+        <is>
+          <t xml:space="preserve">12-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F50">
+        <is>
+          <t xml:space="preserve">MOHAMMED NABEEL N</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G50">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H50">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I50">
+        <is>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J50">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K50">
+        <is>
+          <t xml:space="preserve">visit later</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="65">
+        <v>49</v>
+      </c>
+      <c t="inlineStr" r="B51">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C51">
+        <is>
+          <t xml:space="preserve">SAJIN</t>
+        </is>
+      </c>
+      <c r="D51" s="65">
+        <v>9745123128</v>
+      </c>
+      <c t="inlineStr" r="E51">
+        <is>
+          <t xml:space="preserve">07-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F51">
+        <is>
+          <t xml:space="preserve">Deepu M</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G51">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H51">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I51">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J51">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="65">
+        <v>50</v>
+      </c>
+      <c t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C52">
+        <is>
+          <t xml:space="preserve">SHARATH</t>
+        </is>
+      </c>
+      <c r="D52" s="65">
+        <v>7034340793</v>
+      </c>
+      <c t="inlineStr" r="E52">
+        <is>
+          <t xml:space="preserve">25-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F52">
+        <is>
+          <t xml:space="preserve">Deepu M</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G52">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H52">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I52">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J52">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="65">
+        <v>51</v>
+      </c>
+      <c t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C53">
+        <is>
+          <t xml:space="preserve">HARI SANKAR</t>
+        </is>
+      </c>
+      <c r="D53" s="65">
+        <v>9744670171</v>
+      </c>
+      <c t="inlineStr" r="E53">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F53">
+        <is>
+          <t xml:space="preserve">Akash R</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G53">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H53">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I53">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J53">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="65">
+        <v>52</v>
+      </c>
+      <c t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C54">
+        <is>
+          <t xml:space="preserve">VISHNU</t>
+        </is>
+      </c>
+      <c r="D54" s="65">
+        <v>9074541440</v>
+      </c>
+      <c t="inlineStr" r="E54">
+        <is>
+          <t xml:space="preserve">18-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F54">
+        <is>
+          <t xml:space="preserve">Akash R</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G54">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H54">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I54">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J54">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K54">
+        <is>
+          <t xml:space="preserve">BRIDE DRESS NOT CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="65">
+        <v>53</v>
+      </c>
+      <c t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C55">
+        <is>
+          <t xml:space="preserve">SUBHASH</t>
+        </is>
+      </c>
+      <c r="D55" s="65">
+        <v>9746599394</v>
+      </c>
+      <c t="inlineStr" r="E55">
+        <is>
+          <t xml:space="preserve">11-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F55">
+        <is>
+          <t xml:space="preserve">NIHAL S</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G55">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H55">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I55">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J55">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="65">
+        <v>54</v>
+      </c>
+      <c t="inlineStr" r="B56">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C56">
+        <is>
+          <t xml:space="preserve">praveen</t>
+        </is>
+      </c>
+      <c r="D56" s="65">
+        <v>9809978396</v>
+      </c>
+      <c t="inlineStr" r="E56">
+        <is>
+          <t xml:space="preserve">24-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F56">
+        <is>
+          <t xml:space="preserve">NIHAL S</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G56">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H56">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I56">
+        <is>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J56">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K56">
+        <is>
+          <t xml:space="preserve">will visit in jan 1 st week groom is abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="65">
+        <v>55</v>
+      </c>
+      <c t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C57">
+        <is>
+          <t xml:space="preserve">shahin</t>
+        </is>
+      </c>
+      <c r="D57" s="65">
+        <v>773619706</v>
+      </c>
+      <c t="inlineStr" r="E57">
+        <is>
+          <t xml:space="preserve">01-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F57">
+        <is>
+          <t xml:space="preserve">NIHAL S</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G57">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H57">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I57">
+        <is>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J57">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="65">
+        <v>56</v>
+      </c>
+      <c t="inlineStr" r="B58">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C58">
+        <is>
+          <t xml:space="preserve">joseph</t>
+        </is>
+      </c>
+      <c r="D58" s="65">
+        <v>9207394871</v>
+      </c>
+      <c t="inlineStr" r="E58">
+        <is>
+          <t xml:space="preserve">18-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F58">
+        <is>
+          <t xml:space="preserve">ARJUN G.S</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G58">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H58">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I58">
+        <is>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J58">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K58">
+        <is>
+          <t xml:space="preserve">needed big size 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="65">
+        <v>57</v>
+      </c>
+      <c t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C59">
+        <is>
+          <t xml:space="preserve">midhun</t>
+        </is>
+      </c>
+      <c r="D59" s="65">
+        <v>8157951597</v>
+      </c>
+      <c t="inlineStr" r="E59">
+        <is>
+          <t xml:space="preserve">08-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F59">
+        <is>
+          <t xml:space="preserve">NIHAL S</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G59">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H59">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I59">
+        <is>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J59">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K59">
+        <is>
+          <t xml:space="preserve">need 46 size</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="65">
+        <v>58</v>
+      </c>
+      <c t="inlineStr" r="B60">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C60">
+        <is>
+          <t xml:space="preserve">Arjun</t>
+        </is>
+      </c>
+      <c r="D60" s="65">
+        <v>8075605726</v>
+      </c>
+      <c t="inlineStr" r="E60">
+        <is>
+          <t xml:space="preserve">22-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F60">
+        <is>
+          <t xml:space="preserve">NIHAL S</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G60">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H60">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I60">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J60">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K60">
+        <is>
+          <t xml:space="preserve">will visit if interested</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
